--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="49" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -601,16 +601,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: ， ou</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Plaintiffâ€™s Solicitor.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]26 THE WRIT.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]26 THE WRIT.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L7: isolated marker/symbol line :: 185</t>
@@ -657,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,14 +672,10 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: .â€”"A Defendant is to answer or demur,</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: against you as the Court shall think just upon the plaintiffâ€™s</t>
-        </is>
-      </c>
+          <t>L19: stray/suspicious non-ASCII glyph(s): U+5236 CJK UNIFIED IDEOGRAPH-5236 | isolated marker/symbol line :: 制</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -727,14 +727,10 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Service of the Subp Ã¦ ena is by</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: own showingâ€”(where the defendant is to be served out</t>
-        </is>
-      </c>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -766,12 +762,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -780,21 +776,13 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L129: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ ena is by delivering a copy to the</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of the jurisdiction, add the following words)â€”without</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L28: isolated marker/symbol line :: A</t>
+          <t>L19: stray/suspicious non-ASCII glyph(s): U+5236 CJK UNIFIED IDEOGRAPH-5236 | isolated marker/symbol line :: 制</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -836,16 +824,12 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: memorandum, with these words.â€”" A Defendant is to answer or demur,</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L28: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -892,7 +876,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L98: symbol-only separator/garbage line :: 238;</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -939,7 +923,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L101: symbol-only separator/garbage line :: 391;</t>
+          <t>L98: symbol-only separator/garbage line :: 238;</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -986,7 +970,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: T</t>
+          <t>L101: symbol-only separator/garbage line :: 391;</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -1009,12 +993,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1029,7 +1013,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: e</t>
+          <t>L121: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1057,7 +1041,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1072,7 +1056,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: ,</t>
+          <t>L122: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1095,7 +1079,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1115,7 +1099,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: ~</t>
+          <t>L123: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1158,7 +1142,7 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: X</t>
+          <t>L133: isolated marker/symbol line :: ~</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr"/>
@@ -1201,7 +1185,7 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L143: isolated marker/symbol line :: T</t>
+          <t>L140: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr"/>
@@ -1242,7 +1226,11 @@
       <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="1" t="inlineStr"/>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>L143: isolated marker/symbol line :: T</t>
+        </is>
+      </c>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
